--- a/data/trans_orig/IP16B03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B03-Provincia-trans_orig.xlsx
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
